--- a/data/trans_orig/P1802_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1802_2016_2023-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68107</t>
+          <t>67995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103071</t>
+          <t>102711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97977</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138879</t>
+          <t>136870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176149</t>
+          <t>175521</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227654</t>
+          <t>229715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571729</t>
+          <t>572089</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>606693</t>
+          <t>606805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533960</t>
+          <t>535969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>574862</t>
+          <t>575278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1119985</t>
+          <t>1117924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1171490</t>
+          <t>1172118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141680</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189839</t>
+          <t>190696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191876</t>
+          <t>186226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241601</t>
+          <t>240622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,47 +1124,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>380028</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>342061</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>417940</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>18,4%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>380028</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>345259</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>418933</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>18,4%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>832592</t>
+          <t>831735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>880751</t>
+          <t>880109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>801312</t>
+          <t>802291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>851037</t>
+          <t>856687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,47 +1237,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1578</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1685316</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1647404</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1723283</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>81,6%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1578</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1685316</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1646411</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1720085</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>81,6%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>86855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125821</t>
+          <t>125901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127794</t>
+          <t>128631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172580</t>
+          <t>174992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>227072</t>
+          <t>225783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289482</t>
+          <t>286044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633731</t>
+          <t>633651</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673444</t>
+          <t>672697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>612431</t>
+          <t>610019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657217</t>
+          <t>656380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255081</t>
+          <t>1258519</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317491</t>
+          <t>1318780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109181</t>
+          <t>111679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152906</t>
+          <t>156566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164221</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>213691</t>
+          <t>214922</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>288856</t>
+          <t>289972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>356066</t>
+          <t>357745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>784661</t>
+          <t>781001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>828386</t>
+          <t>825888</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>830088</t>
+          <t>828857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>879558</t>
+          <t>879413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1625280</t>
+          <t>1623601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1692490</t>
+          <t>1691374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>450601</t>
+          <t>447787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>532950</t>
+          <t>530340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>623660</t>
+          <t>621069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>717621</t>
+          <t>719257</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1094059</t>
+          <t>1093456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1227221</t>
+          <t>1223456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2861400</t>
+          <t>2864010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2943749</t>
+          <t>2946563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2826921</t>
+          <t>2825285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2920882</t>
+          <t>2923473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5711671</t>
+          <t>5715436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5844833</t>
+          <t>5845436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>94982</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73475</t>
+          <t>77856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107249</t>
+          <t>113444</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>115066</t>
+          <t>122864</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99860</t>
+          <t>106767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>131279</t>
+          <t>140199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>205205</t>
+          <t>217846</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>181663</t>
+          <t>193367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231718</t>
+          <t>244039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>545302</t>
+          <t>595728</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>528192</t>
+          <t>577266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561966</t>
+          <t>612854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>560686</t>
+          <t>610249</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>544473</t>
+          <t>592914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>575892</t>
+          <t>626346</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1105989</t>
+          <t>1205977</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1079476</t>
+          <t>1179784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1129531</t>
+          <t>1230456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>372269</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>150778</t>
+          <t>112862</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>791436</t>
+          <t>158217</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>137267</t>
+          <t>158424</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>136936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155782</t>
+          <t>177771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>509536</t>
+          <t>292340</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289151</t>
+          <t>261743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1047548</t>
+          <t>322870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>820595</t>
+          <t>915001</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401428</t>
+          <t>890700</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1042086</t>
+          <t>936055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>820839</t>
+          <t>912414</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>802324</t>
+          <t>893067</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>836989</t>
+          <t>933902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1641435</t>
+          <t>1827415</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1103423</t>
+          <t>1796885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1861820</t>
+          <t>1858012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100513</t>
+          <t>108529</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82272</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122337</t>
+          <t>131596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>135352</t>
+          <t>161801</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72780</t>
+          <t>141129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>182692</t>
+          <t>185179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>235865</t>
+          <t>270329</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149855</t>
+          <t>241252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286486</t>
+          <t>300679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>603420</t>
+          <t>693670</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>581596</t>
+          <t>670603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621661</t>
+          <t>711243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>795491</t>
+          <t>647822</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>748151</t>
+          <t>624444</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>858063</t>
+          <t>668494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1398912</t>
+          <t>1341493</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1348291</t>
+          <t>1311143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1484922</t>
+          <t>1370570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703933</t>
+          <t>802199</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703933</t>
+          <t>802199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703933</t>
+          <t>802199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>930843</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930843</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>930843</t>
+          <t>809623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634777</t>
+          <t>1611822</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634777</t>
+          <t>1611822</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634777</t>
+          <t>1611822</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>193491</t>
+          <t>196607</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169098</t>
+          <t>172507</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219655</t>
+          <t>224723</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>241085</t>
+          <t>256644</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194168</t>
+          <t>233942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>269353</t>
+          <t>283135</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,17 +3772,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>434576</t>
+          <t>453251</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>385470</t>
+          <t>421921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>472788</t>
+          <t>489385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>732627</t>
+          <t>792659</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>706463</t>
+          <t>764543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>757020</t>
+          <t>816759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>853169</t>
+          <t>861713</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>824901</t>
+          <t>835222</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>900086</t>
+          <t>884415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1585796</t>
+          <t>1654371</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1547584</t>
+          <t>1618237</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1634902</t>
+          <t>1685701</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926118</t>
+          <t>989266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926118</t>
+          <t>989266</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926118</t>
+          <t>989266</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2020372</t>
+          <t>2107622</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2020372</t>
+          <t>2107622</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2020372</t>
+          <t>2107622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>535648</t>
+          <t>492282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1357470</t>
+          <t>581716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>628769</t>
+          <t>699733</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>519238</t>
+          <t>660448</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>689500</t>
+          <t>745858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1385181</t>
+          <t>1233766</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1146383</t>
+          <t>1170974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2120306</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2701945</t>
+          <t>2997057</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2100887</t>
+          <t>2949375</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2922709</t>
+          <t>3038809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3030187</t>
+          <t>3032198</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2969456</t>
+          <t>2986073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3139718</t>
+          <t>3071483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5732132</t>
+          <t>6029256</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4997007</t>
+          <t>5972558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5970930</t>
+          <t>6092048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458357</t>
+          <t>3531091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658956</t>
+          <t>3731931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117313</t>
+          <t>7263022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
